--- a/data/samsung-service-prices.xlsx
+++ b/data/samsung-service-prices.xlsx
@@ -5,15 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/89fe5ae0d6b51d32/Dokumenty/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamd\Github\maro_web\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1263232-3ABA-4269-8F4C-7B1722B30230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D98B229-726E-4510-985A-5E329587C127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{7086E827-2BEE-473B-BA1A-5CAD5929993F}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="galaxy-a" sheetId="1" r:id="rId1"/>
+    <sheet name="galaxy-m" sheetId="2" r:id="rId2"/>
+    <sheet name="galaxy-note" sheetId="3" r:id="rId3"/>
+    <sheet name="galaxy-s" sheetId="4" r:id="rId4"/>
+    <sheet name="galaxy-z" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,15 +39,50 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="8">
+  <si>
+    <t>ProductName</t>
+  </si>
+  <si>
+    <t>displej</t>
+  </si>
+  <si>
+    <t>bateria</t>
+  </si>
+  <si>
+    <t>nabijanie</t>
+  </si>
+  <si>
+    <t>tekutina</t>
+  </si>
+  <si>
+    <t>diagnostika</t>
+  </si>
+  <si>
+    <t>inyproblem</t>
+  </si>
+  <si>
+    <t>backglass</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -67,8 +106,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -403,9 +443,225 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68E7282C-F129-45FA-83C9-ABA740391124}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="5" max="5" width="11.140625" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" customWidth="1"/>
+    <col min="13" max="13" width="11.140625" customWidth="1"/>
+    <col min="14" max="14" width="11.85546875" customWidth="1"/>
+    <col min="19" max="19" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B9B2FEE-3C95-42A1-8584-CD1B534DDFB4}">
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" customWidth="1"/>
+    <col min="9" max="9" width="11" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" customWidth="1"/>
+    <col min="14" max="14" width="12.42578125" customWidth="1"/>
+    <col min="16" max="16" width="10.42578125" customWidth="1"/>
+    <col min="19" max="20" width="11.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE6E7198-150F-4C2D-871F-8E67716203E4}">
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.42578125" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CF61A20-544B-4258-9AF5-8897163C8398}">
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.28515625" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6086A363-4DB7-42D2-BA8D-A020BDF26AE5}">
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/samsung-service-prices.xlsx
+++ b/data/samsung-service-prices.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamd\Github\maro_web\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stano\Documents\mobilflex\dzuris.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D98B229-726E-4510-985A-5E329587C127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC36099-4E3D-4CBA-AEB8-53A4CDD941ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{7086E827-2BEE-473B-BA1A-5CAD5929993F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{7086E827-2BEE-473B-BA1A-5CAD5929993F}"/>
   </bookViews>
   <sheets>
     <sheet name="galaxy-a" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="29">
   <si>
     <t>ProductName</t>
   </si>
@@ -64,6 +64,69 @@
   </si>
   <si>
     <t>backglass</t>
+  </si>
+  <si>
+    <t>galaxy-a-02</t>
+  </si>
+  <si>
+    <t>galaxy-a-02s</t>
+  </si>
+  <si>
+    <t>galaxy-a-03s</t>
+  </si>
+  <si>
+    <t>galaxy-a-04</t>
+  </si>
+  <si>
+    <t>galaxy-a-04s</t>
+  </si>
+  <si>
+    <t>galaxy-a-10</t>
+  </si>
+  <si>
+    <t>galaxy-a-10s</t>
+  </si>
+  <si>
+    <t>galaxy-a-12</t>
+  </si>
+  <si>
+    <t>galaxy-a-13</t>
+  </si>
+  <si>
+    <t>Zadarmo</t>
+  </si>
+  <si>
+    <t>Na otázku</t>
+  </si>
+  <si>
+    <t>galaxy-a-14-5g</t>
+  </si>
+  <si>
+    <t>galaxy-a-21s</t>
+  </si>
+  <si>
+    <t>galaxy-a-22-5g</t>
+  </si>
+  <si>
+    <t>galaxy-a-23-5g</t>
+  </si>
+  <si>
+    <t>galaxy-m-11</t>
+  </si>
+  <si>
+    <t>galaxy-m-12</t>
+  </si>
+  <si>
+    <t>galaxy-m-13</t>
+  </si>
+  <si>
+    <t>galaxy-note-8</t>
+  </si>
+  <si>
+    <t>galaxy-note-9</t>
+  </si>
+  <si>
+    <t>galaxy-note-10-lite</t>
   </si>
 </sst>
 </file>
@@ -111,7 +174,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normálna" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -127,7 +190,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motív Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -443,22 +506,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68E7282C-F129-45FA-83C9-ABA740391124}">
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H99"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="5" max="5" width="11.140625" customWidth="1"/>
-    <col min="6" max="6" width="13.85546875" customWidth="1"/>
-    <col min="7" max="7" width="12.85546875" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" customWidth="1"/>
-    <col min="13" max="13" width="11.140625" customWidth="1"/>
-    <col min="14" max="14" width="11.85546875" customWidth="1"/>
-    <col min="19" max="19" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="11.109375" customWidth="1"/>
+    <col min="6" max="6" width="13.88671875" customWidth="1"/>
+    <col min="7" max="7" width="12.88671875" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" customWidth="1"/>
+    <col min="9" max="9" width="11.44140625" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" customWidth="1"/>
+    <col min="13" max="13" width="11.109375" customWidth="1"/>
+    <col min="14" max="14" width="11.88671875" customWidth="1"/>
+    <col min="19" max="19" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -484,30 +547,396 @@
         <v>6</v>
       </c>
     </row>
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2">
+        <v>80</v>
+      </c>
+      <c r="C2">
+        <v>55</v>
+      </c>
+      <c r="D2">
+        <v>54</v>
+      </c>
+      <c r="E2">
+        <v>47</v>
+      </c>
+      <c r="F2">
+        <v>30</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>80</v>
+      </c>
+      <c r="C3">
+        <v>51</v>
+      </c>
+      <c r="D3">
+        <v>54</v>
+      </c>
+      <c r="E3">
+        <v>47</v>
+      </c>
+      <c r="F3">
+        <v>30</v>
+      </c>
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>75</v>
+      </c>
+      <c r="C4">
+        <v>51</v>
+      </c>
+      <c r="D4">
+        <v>54</v>
+      </c>
+      <c r="E4">
+        <v>47</v>
+      </c>
+      <c r="F4">
+        <v>30</v>
+      </c>
+      <c r="G4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>80</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>75</v>
+      </c>
+      <c r="C6">
+        <v>51</v>
+      </c>
+      <c r="D6">
+        <v>54</v>
+      </c>
+      <c r="E6">
+        <v>47</v>
+      </c>
+      <c r="F6">
+        <v>30</v>
+      </c>
+      <c r="G6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <v>75</v>
+      </c>
+      <c r="C7">
+        <v>48</v>
+      </c>
+      <c r="D7">
+        <v>54</v>
+      </c>
+      <c r="E7">
+        <v>47</v>
+      </c>
+      <c r="F7">
+        <v>30</v>
+      </c>
+      <c r="G7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8">
+        <v>75</v>
+      </c>
+      <c r="C8">
+        <v>48</v>
+      </c>
+      <c r="D8">
+        <v>54</v>
+      </c>
+      <c r="E8">
+        <v>47</v>
+      </c>
+      <c r="F8">
+        <v>30</v>
+      </c>
+      <c r="G8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9">
+        <v>84</v>
+      </c>
+      <c r="C9">
+        <v>51</v>
+      </c>
+      <c r="D9">
+        <v>55</v>
+      </c>
+      <c r="E9">
+        <v>47</v>
+      </c>
+      <c r="F9">
+        <v>30</v>
+      </c>
+      <c r="G9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10">
+        <v>78</v>
+      </c>
+      <c r="C10">
+        <v>51</v>
+      </c>
+      <c r="D10">
+        <v>52</v>
+      </c>
+      <c r="E10">
+        <v>47</v>
+      </c>
+      <c r="F10">
+        <v>30</v>
+      </c>
+      <c r="G10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11">
+        <v>73</v>
+      </c>
+      <c r="C11">
+        <v>51</v>
+      </c>
+      <c r="D11">
+        <v>51</v>
+      </c>
+      <c r="E11">
+        <v>47</v>
+      </c>
+      <c r="F11">
+        <v>30</v>
+      </c>
+      <c r="G11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12">
+        <v>85</v>
+      </c>
+      <c r="C12">
+        <v>51</v>
+      </c>
+      <c r="D12">
+        <v>52</v>
+      </c>
+      <c r="E12">
+        <v>47</v>
+      </c>
+      <c r="F12">
+        <v>30</v>
+      </c>
+      <c r="G12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13">
+        <v>75</v>
+      </c>
+      <c r="C13">
+        <v>50</v>
+      </c>
+      <c r="D13">
+        <v>51</v>
+      </c>
+      <c r="E13">
+        <v>47</v>
+      </c>
+      <c r="F13">
+        <v>30</v>
+      </c>
+      <c r="G13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14">
+        <v>115</v>
+      </c>
+      <c r="C14">
+        <v>50</v>
+      </c>
+      <c r="D14">
+        <v>60</v>
+      </c>
+      <c r="E14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14">
+        <v>30</v>
+      </c>
+      <c r="G14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="18" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="19" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="23" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="38" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="39" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="41" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="42" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="43" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="45" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="46" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="47" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="49" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="50" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="51" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="53" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="54" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="55" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="57" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="58" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="59" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="61" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="62" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="63" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="65" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="66" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="67" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="69" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="70" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="71" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="73" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="74" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="75" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="77" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="78" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="79" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="81" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="82" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="83" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="85" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="86" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="87" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="89" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="90" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="91" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="93" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="94" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="95" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="97" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="98" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="99" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B9B2FEE-3C95-42A1-8584-CD1B534DDFB4}">
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="4" max="4" width="10.88671875" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="11" max="11" width="13.5703125" customWidth="1"/>
-    <col min="13" max="13" width="10.5703125" customWidth="1"/>
-    <col min="14" max="14" width="12.42578125" customWidth="1"/>
-    <col min="16" max="16" width="10.42578125" customWidth="1"/>
-    <col min="19" max="20" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="13.5546875" customWidth="1"/>
+    <col min="13" max="13" width="10.5546875" customWidth="1"/>
+    <col min="14" max="14" width="12.44140625" customWidth="1"/>
+    <col min="16" max="16" width="10.44140625" customWidth="1"/>
+    <col min="19" max="20" width="11.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -531,6 +960,75 @@
       </c>
       <c r="H1" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2">
+        <v>83</v>
+      </c>
+      <c r="C2">
+        <v>49</v>
+      </c>
+      <c r="D2">
+        <v>54</v>
+      </c>
+      <c r="E2">
+        <v>47</v>
+      </c>
+      <c r="F2">
+        <v>30</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3">
+        <v>85</v>
+      </c>
+      <c r="C3">
+        <v>49</v>
+      </c>
+      <c r="D3">
+        <v>56</v>
+      </c>
+      <c r="E3">
+        <v>47</v>
+      </c>
+      <c r="F3">
+        <v>30</v>
+      </c>
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4">
+        <v>82</v>
+      </c>
+      <c r="C4">
+        <v>50</v>
+      </c>
+      <c r="D4">
+        <v>52</v>
+      </c>
+      <c r="E4">
+        <v>47</v>
+      </c>
+      <c r="F4">
+        <v>30</v>
+      </c>
+      <c r="G4" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -540,16 +1038,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE6E7198-150F-4C2D-871F-8E67716203E4}">
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" customWidth="1"/>
-    <col min="5" max="5" width="12.140625" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.44140625" customWidth="1"/>
+    <col min="5" max="5" width="12.109375" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" customWidth="1"/>
+    <col min="8" max="8" width="13.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -573,6 +1071,75 @@
       </c>
       <c r="H1" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2">
+        <v>210</v>
+      </c>
+      <c r="C2">
+        <v>58</v>
+      </c>
+      <c r="D2">
+        <v>62</v>
+      </c>
+      <c r="E2">
+        <v>55</v>
+      </c>
+      <c r="F2">
+        <v>30</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3">
+        <v>200</v>
+      </c>
+      <c r="C3">
+        <v>58</v>
+      </c>
+      <c r="D3">
+        <v>62</v>
+      </c>
+      <c r="E3">
+        <v>55</v>
+      </c>
+      <c r="F3">
+        <v>30</v>
+      </c>
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4">
+        <v>145</v>
+      </c>
+      <c r="C4">
+        <v>63</v>
+      </c>
+      <c r="D4">
+        <v>65</v>
+      </c>
+      <c r="E4">
+        <v>55</v>
+      </c>
+      <c r="F4">
+        <v>30</v>
+      </c>
+      <c r="G4" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -583,16 +1150,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CF61A20-544B-4258-9AF5-8897163C8398}">
   <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="1" max="1" width="15.33203125" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="5" max="5" width="12.88671875" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" customWidth="1"/>
+    <col min="8" max="8" width="11.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -626,16 +1193,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6086A363-4DB7-42D2-BA8D-A020BDF26AE5}">
   <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" customWidth="1"/>
+    <col min="8" max="8" width="13.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
